--- a/etf_holdings/2026-08-24_common_holdings_all_00981A_00991A_00980A_00982A_00403A_00985A_00992A_00990A.xlsx
+++ b/etf_holdings/2026-08-24_common_holdings_all_00981A_00991A_00980A_00982A_00403A_00985A_00992A_00990A.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10.16%</t>
+          <t>10.12%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -628,7 +628,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>8.87%</t>
+          <t>8.74%</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -641,7 +641,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>17.12%</t>
+          <t>17.19%</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -667,7 +667,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>7.51%</t>
+          <t>7.47%</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -688,12 +688,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>82.15%</t>
+          <t>82.01%</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>10.27%</t>
+          <t>10.25%</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.76%</t>
+          <t>9.43%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>3.73%</t>
+          <t>3.56%</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -775,7 +775,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>5.53%</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>6.30%</t>
+          <t>6.08%</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -822,12 +822,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>43.38%</t>
+          <t>42.51%</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>5.42%</t>
+          <t>5.31%</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6.92%</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>6.78%</t>
+          <t>6.73%</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -909,7 +909,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>4.73%</t>
+          <t>4.79%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>2.41%</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>33.32%</t>
+          <t>33.37%</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.74%</t>
+          <t>4.87%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1030,11 +1030,11 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>817000</v>
+        <v>727000</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.88%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>5.21%</t>
+          <t>5.35%</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>25.57%</t>
+          <t>25.62%</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4.06%</t>
+          <t>4.14%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.86%</t>
         </is>
       </c>
       <c r="R6" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13.48%</t>
+          <t>13.67%</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3.88%</t>
+          <t>3.92%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="R7" t="n">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.82%</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13.47%</t>
+          <t>13.56%</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
